--- a/stories/arbres/ATOM-FAM.SEC.002-08.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cécile range son manteau au vestiaire. Un adulte parle tout bas. Il dit : c'est notre secret. Cécile sent son ventre. C'est serré. C'est un malaise. Cécile a peur. Ce n'est pas une surprise gentille. Cécile marche vers papa, à la porte. Elle prend sa main. Cécile dit : papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Papa dit : merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Cécile le dit aussi à maman. Même leçon, autre lieu. Maman écoute. Cécile se sent plus légère. Raconter à papa ou maman, ça aide.</t>
+          <t>Cécile range son manteau au vestiaire. Un adulte parle tout bas. C'est notre secret. Cécile sent son ventre. C'est serré. C'est un malaise. Cécile a peur. Ce n'est pas une surprise gentille. Cécile marche vers papa, à la porte. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Cécile le dit aussi à maman. Même leçon, autre lieu. Maman écoute. Cécile se sent plus légère. Raconter à papa ou maman, ça aide.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile range son manteau au vestiaire. Un adulte parle tout bas.
+narrateur|C'est notre secret.
+narrateur|Cécile sent son ventre. C'est serré. C'est un malaise. Cécile a peur. Ce n'est pas une surprise gentille. Cécile marche vers papa, à la porte. Elle prend sa main.
+enfant-f|Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute.
+papa|Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Cécile le dit aussi à maman. Même leçon, autre lieu. Maman écoute.
+narrateur|Cécile se sent plus légère. Raconter à papa ou maman, ça aide.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile a peur. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1835,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2002,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2042,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-08.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Cécile se sent plus légère. Raconter à papa ou maman, ça aide.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Cécile a peur. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1680,7 @@
           <t>narrateur|Cécile a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1840,6 +1848,7 @@
           <t>narrateur|Cécile s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2007,6 +2016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2049,6 +2059,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2274,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.SEC.002-08.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cécile raconte ce qui fait peur</t>
+          <t>Mila raconte ce qui fait peur</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Au vestiaire, un adulte parle d'un secret. Mila a peur. Elle le dit à papa, puis à maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cécile range son manteau au vestiaire. Un adulte parle tout bas. C'est notre secret. Cécile sent son ventre. C'est serré. C'est un malaise. Cécile a peur. Ce n'est pas une surprise gentille. Cécile marche vers papa, à la porte. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Cécile le dit aussi à maman. Même leçon, autre lieu. Maman écoute. Cécile se sent plus légère. Raconter à papa ou maman, ça aide.</t>
+          <t>Les gouttières de l'école chantent. Un filet d'eau glisse sur la vitre. Les manteaux sentent la laine mouillée. Des gouttes tombent des capuches. Elles font des ronds dans une flaque. Les crochets de fer cliquettent. Le banc du vestiaire est froid. Le ciré jaune de papa brille un peu. Tu as vu les ronds dans l'eau, Mila ? Oui, papa. Ils grandissent. Le vestiaire sent la pluie. Ton manteau est lourd, hein ? Oui. Il est tout mouillé. En ce moment, Mila range son manteau. Le manteau bleu est humide et froid. Elle le pose sur un crochet. Le crochet tapote le bois. Un adulte parle tout bas, près des casiers. Il parle d'un secret. Mila sent son ventre. C'est serré. C'est un malaise. Mila a peur. Ce n'est pas une surprise gentille. Mila cherche papa des yeux. Papa attend près de la porte. Sa main est grande et ouverte. Mila marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Je t'écoute, Mila. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On raconte à papa ou maman. Tu as fait du bon travail. Tu veux rester près de moi ? Oui, papa. Près de toi. Mila serre la main de papa. Sa main est chaude. Le ventre de Mila se desserre un peu. On rentre à la maison, maintenant ? Oui. Plus tard, la maison sent la soupe. La fenêtre de la cuisine est un peu embuée. Une goutte coule sur la vitre. Maman coupe du pain. Tu as les joues froides, Mila. Tu veux un bout de pain tiède ? Maman, j'ai eu peur. Un adulte a parlé d'un secret. Mon ventre était serré. Je t'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. À papa ou à maman. Bravo, Mila. C'est du bon travail. Tu te sens plus légère, maintenant ? Oui, maman. Un peu. Mila s'assoit près de maman. Papa pose le ciré jaune. Ta main peut rester dans la mienne. D'accord. Le pain sent le chaud. La soupe fume dans l'assiette. On reste ensemble un peu ? Oui. Près de vous. Mila souffle. Son ventre est plus doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,91 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Cécile range son manteau au vestiaire. Un adulte parle tout bas.
-narrateur|C'est notre secret.
-narrateur|Cécile sent son ventre. C'est serré. C'est un malaise. Cécile a peur. Ce n'est pas une surprise gentille. Cécile marche vers papa, à la porte. Elle prend sa main.
-enfant-f|Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute.
-papa|Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Cécile le dit aussi à maman. Même leçon, autre lieu. Maman écoute.
-narrateur|Cécile se sent plus légère. Raconter à papa ou maman, ça aide.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les gouttières de l'école chantent.
+narrateur|Un filet d'eau glisse sur la vitre.
+narrateur|Les manteaux sentent la laine mouillée.
+narrateur|Des gouttes tombent des capuches.
+narrateur|Elles font des ronds dans une flaque.
+narrateur|Les crochets de fer cliquettent.
+narrateur|Le banc du vestiaire est froid.
+narrateur|Le ciré jaune de papa brille un peu.
+papa|Tu as vu les ronds dans l'eau, Mila ?
+enfant-f|Oui, papa.
+enfant-f|Ils grandissent.
+papa|Le vestiaire sent la pluie.
+papa|Ton manteau est lourd, hein ?
+enfant-f|Oui.
+enfant-f|Il est tout mouillé.
+narrateur|En ce moment, Mila range son manteau.
+narrateur|Le manteau bleu est humide et froid.
+narrateur|Elle le pose sur un crochet.
+narrateur|Le crochet tapote le bois.
+narrateur|Un adulte parle tout bas, près des casiers.
+narrateur|Il parle d'un secret.
+narrateur|Mila sent son ventre.
+narrateur|C'est serré.
+narrateur|C'est un malaise.
+narrateur|Mila a peur.
+narrateur|Ce n'est pas une surprise gentille.
+narrateur|Mila cherche papa des yeux.
+narrateur|Papa attend près de la porte.
+narrateur|Sa main est grande et ouverte.
+narrateur|Mila marche vers papa.
+narrateur|Elle prend sa main.
+enfant-f|Papa, un adulte a parlé d'un secret.
+enfant-f|Mon ventre est serré.
+enfant-f|J'ai peur.
+papa|Je t'écoute, Mila.
+papa|Merci de raconter.
+papa|Tu as le droit de le dire.
+papa|Ce qui fait peur se raconte.
+papa|On raconte à papa ou maman.
+papa|Tu as fait du bon travail.
+papa|Tu veux rester près de moi ?
+enfant-f|Oui, papa.
+enfant-f|Près de toi.
+narrateur|Mila serre la main de papa.
+narrateur|Sa main est chaude.
+narrateur|Le ventre de Mila se desserre un peu.
+papa|On rentre à la maison, maintenant ?
+enfant-f|Oui.
+narrateur|Plus tard, la maison sent la soupe.
+narrateur|La fenêtre de la cuisine est un peu embuée.
+narrateur|Une goutte coule sur la vitre.
+narrateur|Maman coupe du pain.
+maman|Tu as les joues froides, Mila.
+maman|Tu veux un bout de pain tiède ?
+enfant-f|Maman, j'ai eu peur.
+enfant-f|Un adulte a parlé d'un secret.
+enfant-f|Mon ventre était serré.
+maman|Je t'écoute.
+maman|Merci de raconter.
+maman|Tu as le droit de le dire.
+maman|Ce qui fait peur se raconte.
+maman|À papa ou à maman.
+maman|Bravo, Mila.
+maman|C'est du bon travail.
+maman|Tu te sens plus légère, maintenant ?
+enfant-f|Oui, maman.
+enfant-f|Un peu.
+narrateur|Mila s'assoit près de maman.
+narrateur|Papa pose le ciré jaune.
+papa|Ta main peut rester dans la mienne.
+enfant-f|D'accord.
+narrateur|Le pain sent le chaud.
+narrateur|La soupe fume dans l'assiette.
+maman|On reste ensemble un peu ?
+enfant-f|Oui.
+enfant-f|Près de vous.
+narrateur|Mila souffle.
+narrateur|Son ventre est plus doux.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>gouttiere,crochets_manteaux</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,7 +1433,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Cécile a peur. Que fait-elle ?</t>
+          <t>Mila a peur. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1505,7 +1593,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Cécile a peur. Que fait-elle ?</t>
+          <t>narrateur|Mila a peur.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1533,7 +1622,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Cécile a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+          <t>Mila a senti le malaise. Elle a marché vers papa. Elle a raconté. Tu as raconté à papa. Puis tu as raconté à maman. Ce qui fait peur se raconte. Bravo, Mila. C'est du bon travail. J'ai raconté. J'avais peur. Oui. À papa ou à maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1677,7 +1766,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Cécile a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+          <t>narrateur|Mila a senti le malaise.
+narrateur|Elle a marché vers papa.
+narrateur|Elle a raconté.
+papa|Tu as raconté à papa.
+maman|Puis tu as raconté à maman.
+maman|Ce qui fait peur se raconte.
+papa|Bravo, Mila.
+papa|C'est du bon travail.
+enfant-f|J'ai raconté.
+enfant-f|J'avais peur.
+maman|Oui.
+maman|À papa ou à maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1705,7 +1805,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Cécile s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+          <t>Mila garde un bout de pain. Il est encore un peu tiède. Tu veux rester à table un moment ? Oui. Près de toi. Je te parle tout bas. Ta main est dans ma main. Mon ventre est plus doux. Oui. Une goutte glisse encore sur la vitre. La soupe fume tout doucement.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1845,7 +1945,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Cécile s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+          <t>narrateur|Mila garde un bout de pain.
+narrateur|Il est encore un peu tiède.
+maman|Tu veux rester à table un moment ?
+enfant-f|Oui.
+enfant-f|Près de toi.
+papa|Je te parle tout bas.
+papa|Ta main est dans ma main.
+enfant-f|Mon ventre est plus doux.
+maman|Oui.
+narrateur|Une goutte glisse encore sur la vitre.
+narrateur|La soupe fume tout doucement.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1873,7 +1983,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai eu peur. J'ai raconté à papa et maman. Bravo. Tu as fait du bon travail. Le ciré jaune sèche près de la porte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2013,7 +2123,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai eu peur.
+enfant-f|J'ai raconté à papa et maman.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le ciré jaune sèche près de la porte.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2035,7 +2150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2073,6 +2188,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-08.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les gouttières de l'école chantent. Un filet d'eau glisse sur la vitre. Les manteaux sentent la laine mouillée. Des gouttes tombent des capuches. Elles font des ronds dans une flaque. Les crochets de fer cliquettent. Le banc du vestiaire est froid. Le ciré jaune de papa brille un peu. Tu as vu les ronds dans l'eau, Mila ? Oui, papa. Ils grandissent. Le vestiaire sent la pluie. Ton manteau est lourd, hein ? Oui. Il est tout mouillé. En ce moment, Mila range son manteau. Le manteau bleu est humide et froid. Elle le pose sur un crochet. Le crochet tapote le bois. Un adulte parle tout bas, près des casiers. Il parle d'un secret. Mila sent son ventre. C'est serré. C'est un malaise. Mila a peur. Ce n'est pas une surprise gentille. Mila cherche papa des yeux. Papa attend près de la porte. Sa main est grande et ouverte. Mila marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Je t'écoute, Mila. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On raconte à papa ou maman. Tu as fait du bon travail. Tu veux rester près de moi ? Oui, papa. Près de toi. Mila serre la main de papa. Sa main est chaude. Le ventre de Mila se desserre un peu. On rentre à la maison, maintenant ? Oui. Plus tard, la maison sent la soupe. La fenêtre de la cuisine est un peu embuée. Une goutte coule sur la vitre. Maman coupe du pain. Tu as les joues froides, Mila. Tu veux un bout de pain tiède ? Maman, j'ai eu peur. Un adulte a parlé d'un secret. Mon ventre était serré. Je t'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. À papa ou à maman. Bravo, Mila. C'est du bon travail. Tu te sens plus légère, maintenant ? Oui, maman. Un peu. Mila s'assoit près de maman. Papa pose le ciré jaune. Ta main peut rester dans la mienne. D'accord. Le pain sent le chaud. La soupe fume dans l'assiette. On reste ensemble un peu ? Oui. Près de vous. Mila souffle. Son ventre est plus doux.</t>
+          <t>Les gouttières de l'école chantent. Un filet d'eau glisse sur la vitre. Les manteaux sentent la laine mouillée. Des gouttes tombent des capuches. Elles font des ronds dans une flaque. Les crochets de fer cliquettent. Le banc du vestiaire est froid. Le ciré jaune de papa brille un peu. Tu as vu les ronds dans l'eau, Mila ? Oui, papa. Ils grandissent. Le vestiaire sent la pluie. Ton manteau est lourd, hein ? Oui. Il est tout mouillé. En ce moment, Mila range son manteau. Le manteau bleu est humide et froid. Elle le pose sur un crochet. Le crochet tapote le bois. Un adulte parle tout bas, près des casiers. Il parle d'un secret. Mila sent son ventre. C'est serré. C'est un malaise. Mila a peur. Ce n'est pas une surprise gentille. Mila cherche papa des yeux. Papa attend près de la porte. Sa main est grande et ouverte. Mila marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Je t'écoute, Mila. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On raconte à papa ou maman. Tu veux rester près de moi ? Oui, papa. Près de toi. Mila serre la main de papa. Sa main est chaude. Le ventre de Mila se desserre un peu. On rentre à la maison, maintenant ? Oui. Plus tard, la maison sent la soupe. La fenêtre de la cuisine est un peu embuée. Une goutte coule sur la vitre. Maman coupe du pain. Tu as les joues froides, Mila. Tu veux un bout de pain tiède ? Maman, j'ai eu peur. Un adulte a parlé d'un secret. Mon ventre était serré. Je t'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. À papa ou à maman. Bravo, Mila. Tu te sens plus légère, maintenant ? Oui, maman. Un peu. Mila s'assoit près de maman. Papa pose le ciré jaune. Ta main peut rester dans la mienne. D'accord. Le pain sent le chaud. La soupe fume dans l'assiette. On reste ensemble un peu ? Oui. Près de vous. Mila souffle. Son ventre est plus doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Cécile range son manteau au vestiaire. Un adulte parle tout bas. Il dit : c'est notre secret. Cécile sent son ventre. C'est serré. C'est un malaise. Cécile a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Ce n'est pas une surprise gentille. Cécile marche vers papa, à la porte. Elle prend sa main. Cécile dit : papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Papa dit : merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Cécile le dit aussi à maman. Même leçon, autre lieu. Maman écoute. Cécile se sent plus légère. Raconter à papa ou maman, ça aide.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les gouttières de l'école chantent. Un filet d'eau glisse sur la vitre. Les manteaux sentent la laine mouillée. Des gouttes tombent des capuches. Elles font des ronds dans une flaque. Les crochets de fer cliquettent. Le banc du vestiaire est froid. Le ciré jaune de papa brille un peu. Tu as vu les ronds dans l'eau, Mila ? Oui, papa. Ils grandissent. Le vestiaire sent la pluie. Ton manteau est lourd, hein ? Oui. Il est tout mouillé. En ce moment, Mila range son manteau. Le manteau bleu est humide et froid. Elle le pose sur un crochet. Le crochet tapote le bois. Un adulte parle tout bas, près des casiers. Il parle d'un secret. Mila sent son ventre. C'est serré. C'est un malaise. Mila a peur. Ce n'est pas une surprise gentille. Mila cherche papa des yeux. Papa attend près de la porte. Sa main est grande et ouverte. Mila marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Je t'écoute, Mila. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On raconte à papa ou maman. Tu veux rester près de moi ? Oui, papa. Près de toi. Mila serre la main de papa. Sa main est chaude. Le ventre de Mila se desserre un peu. On rentre à la maison, maintenant ? Oui. Plus tard, la maison sent la soupe. La fenêtre de la cuisine est un peu embuée. Une goutte coule sur la vitre. Maman coupe du pain. Tu as les joues froides, Mila. Tu veux un bout de pain tiède ? Maman, j'ai eu peur. Un adulte a parlé d'un secret. Mon ventre était serré. Je t'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. À papa ou à maman. Bravo, Mila. Tu te sens plus légère, maintenant ? Oui, maman. Un peu. Mila s'assoit près de maman. Papa pose le ciré jaune. Ta main peut rester dans la mienne. D'accord. Le pain sent le chaud. La soupe fume dans l'assiette. On reste ensemble un peu ? Oui. Près de vous. Mila souffle. Son ventre est plus doux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1363,7 +1363,6 @@
 papa|Tu as le droit de le dire.
 papa|Ce qui fait peur se raconte.
 papa|On raconte à papa ou maman.
-papa|Tu as fait du bon travail.
 papa|Tu veux rester près de moi ?
 enfant-f|Oui, papa.
 enfant-f|Près de toi.
@@ -1387,7 +1386,6 @@
 maman|Ce qui fait peur se raconte.
 maman|À papa ou à maman.
 maman|Bravo, Mila.
-maman|C'est du bon travail.
 maman|Tu te sens plus légère, maintenant ?
 enfant-f|Oui, maman.
 enfant-f|Un peu.
@@ -1438,7 +1436,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Cécile a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a peur. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1597,7 +1595,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1622,12 +1619,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a senti le malaise. Elle a marché vers papa. Elle a raconté. Tu as raconté à papa. Puis tu as raconté à maman. Ce qui fait peur se raconte. Bravo, Mila. C'est du bon travail. J'ai raconté. J'avais peur. Oui. À papa ou à maman.</t>
+          <t>Mila a senti le malaise. Elle a marché vers papa. Elle a raconté. Tu as raconté à papa. Puis tu as raconté à maman. Ce qui fait peur se raconte. Bravo, Mila. J'ai raconté. J'avais peur. Oui. À papa ou à maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Cécile a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt; se raconte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a senti le malaise. Elle a marché vers papa. Elle a raconté. Tu as raconté à papa. Puis tu as raconté à maman. Ce qui fait peur se raconte. Bravo, Mila. J'ai raconté. J'avais peur. Oui. À papa ou à maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1773,14 +1770,12 @@
 maman|Puis tu as raconté à maman.
 maman|Ce qui fait peur se raconte.
 papa|Bravo, Mila.
-papa|C'est du bon travail.
 enfant-f|J'ai raconté.
 enfant-f|J'avais peur.
 maman|Oui.
 maman|À papa ou à maman.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1810,7 +1805,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Cécile s'assoit près de maman. Papa est là aussi. Sa &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; est chaude.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila garde un bout de pain. Il est encore un peu tiède. Tu veux rester à table un moment ? Oui. Près de toi. Je te parle tout bas. Ta main est dans ma main. Mon ventre est plus doux. Oui. Une goutte glisse encore sur la vitre. La soupe fume tout doucement.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1958,7 +1953,6 @@
 narrateur|La soupe fume tout doucement.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1983,12 +1977,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai eu peur. J'ai raconté à papa et maman. Bravo. Tu as fait du bon travail. Le ciré jaune sèche près de la porte. L'histoire est finie.</t>
+          <t>J'ai eu peur. J'ai raconté à papa et maman. Bravo. Le ciré jaune sèche près de la porte.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai eu peur. J'ai raconté à papa et maman. Bravo. Le ciré jaune sèche près de la porte.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2126,12 +2120,9 @@
           <t>enfant-f|J'ai eu peur.
 enfant-f|J'ai raconté à papa et maman.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le ciré jaune sèche près de la porte.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le ciré jaune sèche près de la porte.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2150,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2195,6 +2186,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-08.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cécile, papa, maman</t>
+          <t>Mila, papa, maman</t>
         </is>
       </c>
     </row>
